--- a/data/processed/y_test.xlsx
+++ b/data/processed/y_test.xlsx
@@ -527,7 +527,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21">
@@ -547,7 +547,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25">
@@ -807,7 +807,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77">
@@ -947,12 +947,12 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>334</v>
+        <v>466</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106">
@@ -967,7 +967,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>334</v>
+        <v>615</v>
       </c>
     </row>
     <row r="134">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>334</v>
+        <v>379</v>
       </c>
     </row>
     <row r="139">
@@ -1197,7 +1197,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="155">
@@ -1212,7 +1212,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="158">
@@ -1322,7 +1322,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>334</v>
+        <v>489</v>
       </c>
     </row>
     <row r="180">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>334</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="192">
@@ -1432,7 +1432,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>334</v>
+        <v>481</v>
       </c>
     </row>
     <row r="202">
@@ -1447,7 +1447,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="205">
@@ -1522,7 +1522,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="220">
@@ -1547,7 +1547,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>334</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="225">
@@ -1602,7 +1602,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="236">
@@ -1722,7 +1722,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>334</v>
+        <v>398</v>
       </c>
     </row>
     <row r="260">
@@ -1757,7 +1757,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>334</v>
+        <v>649</v>
       </c>
     </row>
     <row r="267">
@@ -2167,7 +2167,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="349">
@@ -2177,7 +2177,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="351">
@@ -2252,7 +2252,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="366">
@@ -2282,12 +2282,12 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>334</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="373">
@@ -2502,7 +2502,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>334</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="416">
@@ -2697,7 +2697,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="455">
@@ -2757,7 +2757,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="467">
@@ -2897,7 +2897,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="495">
@@ -3077,7 +3077,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="531">
@@ -3157,7 +3157,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="547">
@@ -3167,7 +3167,7 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="549">
@@ -3187,12 +3187,12 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>334</v>
+        <v>418</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>334</v>
+        <v>390</v>
       </c>
     </row>
     <row r="554">
@@ -3237,7 +3237,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="563">
@@ -3467,7 +3467,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="609">
@@ -3527,7 +3527,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>334</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="621">
@@ -3562,7 +3562,7 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="628">
@@ -3697,7 +3697,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>334</v>
+        <v>498</v>
       </c>
     </row>
     <row r="655">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>334</v>
+        <v>590</v>
       </c>
     </row>
     <row r="668">
@@ -4072,7 +4072,7 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="730">
@@ -4087,7 +4087,7 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>334</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="733">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="749">
@@ -4237,12 +4237,12 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>334</v>
+        <v>372</v>
       </c>
     </row>
     <row r="764">
@@ -4582,7 +4582,7 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="832">
@@ -4637,7 +4637,7 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>334</v>
+        <v>549</v>
       </c>
     </row>
     <row r="843">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="865">
@@ -4757,7 +4757,7 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="867">
@@ -4882,7 +4882,7 @@
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="892">
@@ -5057,7 +5057,7 @@
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>334</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="927">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="945">
@@ -5167,7 +5167,7 @@
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>334</v>
+        <v>428</v>
       </c>
     </row>
     <row r="949">
@@ -5282,12 +5282,12 @@
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>334</v>
+        <v>615</v>
       </c>
     </row>
     <row r="973">
@@ -5337,7 +5337,7 @@
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="983">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>334</v>
+        <v>714</v>
       </c>
     </row>
     <row r="988">
@@ -5667,7 +5667,7 @@
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>334</v>
+        <v>950</v>
       </c>
     </row>
     <row r="1049">
@@ -5692,7 +5692,7 @@
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1054">
@@ -5717,7 +5717,7 @@
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="1059">
@@ -5907,7 +5907,7 @@
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>334</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1097">
@@ -5967,7 +5967,7 @@
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1109">
@@ -5992,7 +5992,7 @@
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>334</v>
+        <v>649</v>
       </c>
     </row>
     <row r="1114">
@@ -6117,7 +6117,7 @@
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1139">
@@ -6162,7 +6162,7 @@
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1148">
@@ -6277,7 +6277,7 @@
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>334</v>
+        <v>370</v>
       </c>
     </row>
     <row r="1171">
@@ -6367,12 +6367,12 @@
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1190">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>334</v>
+        <v>409</v>
       </c>
     </row>
     <row r="1196">
@@ -6452,7 +6452,7 @@
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>334</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1206">
@@ -6467,7 +6467,7 @@
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>334</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1209">
@@ -6502,7 +6502,7 @@
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>334</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1216">
@@ -6572,7 +6572,7 @@
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>334</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1230">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1258">
@@ -6737,7 +6737,7 @@
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1263">
@@ -6922,7 +6922,7 @@
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1300">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1304">
@@ -7072,7 +7072,7 @@
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1330">
@@ -7127,7 +7127,7 @@
     </row>
     <row r="1340">
       <c r="A1340" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1341">
@@ -7222,7 +7222,7 @@
     </row>
     <row r="1359">
       <c r="A1359" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="1360">
@@ -7477,7 +7477,7 @@
     </row>
     <row r="1410">
       <c r="A1410" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1411">
@@ -7537,7 +7537,7 @@
     </row>
     <row r="1422">
       <c r="A1422" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1423">
@@ -7622,7 +7622,7 @@
     </row>
     <row r="1439">
       <c r="A1439" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1440">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="1454">
       <c r="A1454" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1455">
@@ -7722,12 +7722,12 @@
     </row>
     <row r="1459">
       <c r="A1459" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1461">
@@ -7747,7 +7747,7 @@
     </row>
     <row r="1464">
       <c r="A1464" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1465">
@@ -7777,7 +7777,7 @@
     </row>
     <row r="1470">
       <c r="A1470" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1471">
@@ -7822,7 +7822,7 @@
     </row>
     <row r="1479">
       <c r="A1479" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1480">
@@ -7862,7 +7862,7 @@
     </row>
     <row r="1487">
       <c r="A1487" t="n">
-        <v>334</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1488">
@@ -7912,7 +7912,7 @@
     </row>
     <row r="1497">
       <c r="A1497" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1498">
@@ -8087,7 +8087,7 @@
     </row>
     <row r="1532">
       <c r="A1532" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1533">
@@ -8232,7 +8232,7 @@
     </row>
     <row r="1561">
       <c r="A1561" t="n">
-        <v>334</v>
+        <v>850</v>
       </c>
     </row>
     <row r="1562">
@@ -8287,7 +8287,7 @@
     </row>
     <row r="1572">
       <c r="A1572" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1573">
@@ -8377,7 +8377,7 @@
     </row>
     <row r="1590">
       <c r="A1590" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1591">
@@ -8407,7 +8407,7 @@
     </row>
     <row r="1596">
       <c r="A1596" t="n">
-        <v>334</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1597">
@@ -8602,12 +8602,12 @@
     </row>
     <row r="1635">
       <c r="A1635" t="n">
-        <v>334</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1637">
@@ -8652,7 +8652,7 @@
     </row>
     <row r="1645">
       <c r="A1645" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1646">
@@ -8872,7 +8872,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1690">
@@ -8987,7 +8987,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1713">
@@ -9052,7 +9052,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1726">
@@ -9187,7 +9187,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1753">
@@ -9202,7 +9202,7 @@
     </row>
     <row r="1755">
       <c r="A1755" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1756">
@@ -9312,7 +9312,7 @@
     </row>
     <row r="1777">
       <c r="A1777" t="n">
-        <v>334</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1778">
@@ -9372,7 +9372,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="n">
-        <v>334</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1790">
@@ -9402,7 +9402,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1796">
@@ -9437,12 +9437,12 @@
     </row>
     <row r="1802">
       <c r="A1802" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="1803">
       <c r="A1803" t="n">
-        <v>334</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1804">
@@ -9462,7 +9462,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1808">
@@ -9502,7 +9502,7 @@
     </row>
     <row r="1815">
       <c r="A1815" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1816">
@@ -9567,7 +9567,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1829">
@@ -9582,7 +9582,7 @@
     </row>
     <row r="1831">
       <c r="A1831" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1832">
@@ -9647,7 +9647,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="n">
-        <v>334</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1845">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="1868">
       <c r="A1868" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1869">
@@ -9802,7 +9802,7 @@
     </row>
     <row r="1875">
       <c r="A1875" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1876">
@@ -10047,7 +10047,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="n">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1925">
@@ -10197,7 +10197,7 @@
     </row>
     <row r="1954">
       <c r="A1954" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1955">
@@ -10227,12 +10227,12 @@
     </row>
     <row r="1960">
       <c r="A1960" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1961">
       <c r="A1961" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1962">
@@ -10407,7 +10407,7 @@
     </row>
     <row r="1996">
       <c r="A1996" t="n">
-        <v>334</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1997">
@@ -10452,12 +10452,12 @@
     </row>
     <row r="2005">
       <c r="A2005" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2006">
       <c r="A2006" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2007">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="2021">
       <c r="A2021" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2022">
@@ -10732,7 +10732,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2062">
@@ -10802,7 +10802,7 @@
     </row>
     <row r="2075">
       <c r="A2075" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2076">
@@ -10812,7 +10812,7 @@
     </row>
     <row r="2077">
       <c r="A2077" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2078">
@@ -10852,7 +10852,7 @@
     </row>
     <row r="2085">
       <c r="A2085" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2086">
@@ -11027,7 +11027,7 @@
     </row>
     <row r="2120">
       <c r="A2120" t="n">
-        <v>334</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="2121">
@@ -11077,7 +11077,7 @@
     </row>
     <row r="2130">
       <c r="A2130" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2131">
@@ -11217,12 +11217,12 @@
     </row>
     <row r="2158">
       <c r="A2158" t="n">
-        <v>334</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2159">
       <c r="A2159" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2160">
@@ -11262,7 +11262,7 @@
     </row>
     <row r="2167">
       <c r="A2167" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2168">
@@ -11422,7 +11422,7 @@
     </row>
     <row r="2199">
       <c r="A2199" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2200">
@@ -11532,7 +11532,7 @@
     </row>
     <row r="2221">
       <c r="A2221" t="n">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2222">
@@ -11567,7 +11567,7 @@
     </row>
     <row r="2228">
       <c r="A2228" t="n">
-        <v>334</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2229">
@@ -11612,7 +11612,7 @@
     </row>
     <row r="2237">
       <c r="A2237" t="n">
-        <v>334</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2238">
@@ -11672,7 +11672,7 @@
     </row>
     <row r="2249">
       <c r="A2249" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2250">
@@ -11682,7 +11682,7 @@
     </row>
     <row r="2251">
       <c r="A2251" t="n">
-        <v>334</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="2252">
@@ -11752,7 +11752,7 @@
     </row>
     <row r="2265">
       <c r="A2265" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2266">
@@ -11837,7 +11837,7 @@
     </row>
     <row r="2282">
       <c r="A2282" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2283">
@@ -11867,7 +11867,7 @@
     </row>
     <row r="2288">
       <c r="A2288" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2289">
@@ -11947,7 +11947,7 @@
     </row>
     <row r="2304">
       <c r="A2304" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2305">
@@ -12012,7 +12012,7 @@
     </row>
     <row r="2317">
       <c r="A2317" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2318">
@@ -12057,7 +12057,7 @@
     </row>
     <row r="2326">
       <c r="A2326" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2327">
@@ -12227,7 +12227,7 @@
     </row>
     <row r="2360">
       <c r="A2360" t="n">
-        <v>334</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2361">
@@ -12442,7 +12442,7 @@
     </row>
     <row r="2403">
       <c r="A2403" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2404">
@@ -12517,7 +12517,7 @@
     </row>
     <row r="2418">
       <c r="A2418" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2419">
@@ -12617,7 +12617,7 @@
     </row>
     <row r="2438">
       <c r="A2438" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="2439">
@@ -12807,7 +12807,7 @@
     </row>
     <row r="2476">
       <c r="A2476" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2477">
@@ -12827,7 +12827,7 @@
     </row>
     <row r="2480">
       <c r="A2480" t="n">
-        <v>334</v>
+        <v>999</v>
       </c>
     </row>
     <row r="2481">
@@ -12977,7 +12977,7 @@
     </row>
     <row r="2510">
       <c r="A2510" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2511">
@@ -13072,12 +13072,12 @@
     </row>
     <row r="2529">
       <c r="A2529" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2530">
       <c r="A2530" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="2531">
@@ -13867,12 +13867,12 @@
     </row>
     <row r="2688">
       <c r="A2688" t="n">
-        <v>334</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2689">
       <c r="A2689" t="n">
-        <v>334</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="2690">
@@ -14072,7 +14072,7 @@
     </row>
     <row r="2729">
       <c r="A2729" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2730">
@@ -14087,7 +14087,7 @@
     </row>
     <row r="2732">
       <c r="A2732" t="n">
-        <v>334</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2733">
@@ -14272,7 +14272,7 @@
     </row>
     <row r="2769">
       <c r="A2769" t="n">
-        <v>334</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2770">
@@ -14367,7 +14367,7 @@
     </row>
     <row r="2788">
       <c r="A2788" t="n">
-        <v>334</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2789">
@@ -14512,7 +14512,7 @@
     </row>
     <row r="2817">
       <c r="A2817" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2818">
@@ -14582,7 +14582,7 @@
     </row>
     <row r="2831">
       <c r="A2831" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2832">
@@ -14617,7 +14617,7 @@
     </row>
     <row r="2838">
       <c r="A2838" t="n">
-        <v>334</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2839">
@@ -14657,7 +14657,7 @@
     </row>
     <row r="2846">
       <c r="A2846" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2847">
@@ -14692,7 +14692,7 @@
     </row>
     <row r="2853">
       <c r="A2853" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2854">
@@ -14702,7 +14702,7 @@
     </row>
     <row r="2855">
       <c r="A2855" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2856">
@@ -14777,7 +14777,7 @@
     </row>
     <row r="2870">
       <c r="A2870" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2871">
@@ -15077,7 +15077,7 @@
     </row>
     <row r="2930">
       <c r="A2930" t="n">
-        <v>334</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2931">
@@ -15202,7 +15202,7 @@
     </row>
     <row r="2955">
       <c r="A2955" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="2956">
@@ -15237,7 +15237,7 @@
     </row>
     <row r="2962">
       <c r="A2962" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2963">
@@ -15257,7 +15257,7 @@
     </row>
     <row r="2966">
       <c r="A2966" t="n">
-        <v>334</v>
+        <v>899</v>
       </c>
     </row>
     <row r="2967">
@@ -15407,7 +15407,7 @@
     </row>
     <row r="2996">
       <c r="A2996" t="n">
-        <v>334</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2997">
@@ -15437,7 +15437,7 @@
     </row>
     <row r="3002">
       <c r="A3002" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3003">
@@ -15452,7 +15452,7 @@
     </row>
     <row r="3005">
       <c r="A3005" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3006">
@@ -15477,7 +15477,7 @@
     </row>
     <row r="3010">
       <c r="A3010" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3011">
@@ -15537,7 +15537,7 @@
     </row>
     <row r="3022">
       <c r="A3022" t="n">
-        <v>334</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3023">
@@ -15827,7 +15827,7 @@
     </row>
     <row r="3080">
       <c r="A3080" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3081">
@@ -15872,7 +15872,7 @@
     </row>
     <row r="3089">
       <c r="A3089" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3090">
@@ -15902,7 +15902,7 @@
     </row>
     <row r="3095">
       <c r="A3095" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3096">
@@ -16057,7 +16057,7 @@
     </row>
     <row r="3126">
       <c r="A3126" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3127">
@@ -16072,7 +16072,7 @@
     </row>
     <row r="3129">
       <c r="A3129" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3130">
@@ -16097,7 +16097,7 @@
     </row>
     <row r="3134">
       <c r="A3134" t="n">
-        <v>334</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3135">
@@ -16207,7 +16207,7 @@
     </row>
     <row r="3156">
       <c r="A3156" t="n">
-        <v>334</v>
+        <v>860</v>
       </c>
     </row>
     <row r="3157">
@@ -16327,7 +16327,7 @@
     </row>
     <row r="3180">
       <c r="A3180" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3181">
@@ -16412,7 +16412,7 @@
     </row>
     <row r="3197">
       <c r="A3197" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3198">
@@ -16547,7 +16547,7 @@
     </row>
     <row r="3224">
       <c r="A3224" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3225">
@@ -16687,7 +16687,7 @@
     </row>
     <row r="3252">
       <c r="A3252" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3253">
@@ -16707,12 +16707,12 @@
     </row>
     <row r="3256">
       <c r="A3256" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3257">
       <c r="A3257" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3258">
@@ -16737,7 +16737,7 @@
     </row>
     <row r="3262">
       <c r="A3262" t="n">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3263">
@@ -16812,7 +16812,7 @@
     </row>
     <row r="3277">
       <c r="A3277" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3278">
@@ -16902,7 +16902,7 @@
     </row>
     <row r="3295">
       <c r="A3295" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3296">
@@ -16932,7 +16932,7 @@
     </row>
     <row r="3301">
       <c r="A3301" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3302">
@@ -17062,7 +17062,7 @@
     </row>
     <row r="3327">
       <c r="A3327" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3328">
@@ -17157,7 +17157,7 @@
     </row>
     <row r="3346">
       <c r="A3346" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3347">
@@ -17177,7 +17177,7 @@
     </row>
     <row r="3350">
       <c r="A3350" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3351">
@@ -17202,7 +17202,7 @@
     </row>
     <row r="3355">
       <c r="A3355" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3356">
@@ -17372,7 +17372,7 @@
     </row>
     <row r="3389">
       <c r="A3389" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3390">
@@ -17392,12 +17392,12 @@
     </row>
     <row r="3393">
       <c r="A3393" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3394">
       <c r="A3394" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3395">
@@ -17432,7 +17432,7 @@
     </row>
     <row r="3401">
       <c r="A3401" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3402">
@@ -17497,7 +17497,7 @@
     </row>
     <row r="3414">
       <c r="A3414" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3415">
@@ -17612,7 +17612,7 @@
     </row>
     <row r="3437">
       <c r="A3437" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3438">
@@ -17697,7 +17697,7 @@
     </row>
     <row r="3454">
       <c r="A3454" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3455">
@@ -17757,7 +17757,7 @@
     </row>
     <row r="3466">
       <c r="A3466" t="n">
-        <v>334</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3467">
@@ -17782,7 +17782,7 @@
     </row>
     <row r="3471">
       <c r="A3471" t="n">
-        <v>334</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3472">
@@ -17812,7 +17812,7 @@
     </row>
     <row r="3477">
       <c r="A3477" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3478">
@@ -18012,7 +18012,7 @@
     </row>
     <row r="3517">
       <c r="A3517" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3518">
@@ -18032,7 +18032,7 @@
     </row>
     <row r="3521">
       <c r="A3521" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3522">
@@ -18117,7 +18117,7 @@
     </row>
     <row r="3538">
       <c r="A3538" t="n">
-        <v>334</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3539">
@@ -18282,7 +18282,7 @@
     </row>
     <row r="3571">
       <c r="A3571" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3572">
@@ -18382,7 +18382,7 @@
     </row>
     <row r="3591">
       <c r="A3591" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3592">
@@ -18407,7 +18407,7 @@
     </row>
     <row r="3596">
       <c r="A3596" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3597">
@@ -18552,12 +18552,12 @@
     </row>
     <row r="3625">
       <c r="A3625" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3626">
       <c r="A3626" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3627">
@@ -18587,7 +18587,7 @@
     </row>
     <row r="3632">
       <c r="A3632" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3633">
@@ -18777,7 +18777,7 @@
     </row>
     <row r="3670">
       <c r="A3670" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3671">
@@ -18892,7 +18892,7 @@
     </row>
     <row r="3693">
       <c r="A3693" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3694">
@@ -18967,7 +18967,7 @@
     </row>
     <row r="3708">
       <c r="A3708" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3709">
@@ -19152,7 +19152,7 @@
     </row>
     <row r="3745">
       <c r="A3745" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3746">
@@ -19202,7 +19202,7 @@
     </row>
     <row r="3755">
       <c r="A3755" t="n">
-        <v>334</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3756">
@@ -19212,7 +19212,7 @@
     </row>
     <row r="3757">
       <c r="A3757" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3758">
@@ -19272,7 +19272,7 @@
     </row>
     <row r="3769">
       <c r="A3769" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3770">
@@ -19312,7 +19312,7 @@
     </row>
     <row r="3777">
       <c r="A3777" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3778">
@@ -19322,7 +19322,7 @@
     </row>
     <row r="3779">
       <c r="A3779" t="n">
-        <v>334</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3780">
@@ -19347,7 +19347,7 @@
     </row>
     <row r="3784">
       <c r="A3784" t="n">
-        <v>334</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3785">
@@ -19457,7 +19457,7 @@
     </row>
     <row r="3806">
       <c r="A3806" t="n">
-        <v>334</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3807">
@@ -19482,7 +19482,7 @@
     </row>
     <row r="3811">
       <c r="A3811" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3812">
@@ -19832,7 +19832,7 @@
     </row>
     <row r="3881">
       <c r="A3881" t="n">
-        <v>334</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3882">
@@ -19857,7 +19857,7 @@
     </row>
     <row r="3886">
       <c r="A3886" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3887">
@@ -19892,7 +19892,7 @@
     </row>
     <row r="3893">
       <c r="A3893" t="n">
-        <v>334</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3894">
@@ -19912,7 +19912,7 @@
     </row>
     <row r="3897">
       <c r="A3897" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3898">
@@ -20012,7 +20012,7 @@
     </row>
     <row r="3917">
       <c r="A3917" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3918">
@@ -20077,7 +20077,7 @@
     </row>
     <row r="3930">
       <c r="A3930" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3931">
@@ -20132,7 +20132,7 @@
     </row>
     <row r="3941">
       <c r="A3941" t="n">
-        <v>334</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3942">
@@ -20167,7 +20167,7 @@
     </row>
     <row r="3948">
       <c r="A3948" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3949">
@@ -20177,7 +20177,7 @@
     </row>
     <row r="3950">
       <c r="A3950" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3951">
@@ -20277,7 +20277,7 @@
     </row>
     <row r="3970">
       <c r="A3970" t="n">
-        <v>334</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="3971">
@@ -20307,7 +20307,7 @@
     </row>
     <row r="3976">
       <c r="A3976" t="n">
-        <v>334</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3977">
@@ -20632,7 +20632,7 @@
     </row>
     <row r="4041">
       <c r="A4041" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4042">
@@ -20647,7 +20647,7 @@
     </row>
     <row r="4044">
       <c r="A4044" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4045">
@@ -20757,7 +20757,7 @@
     </row>
     <row r="4066">
       <c r="A4066" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4067">
@@ -20822,7 +20822,7 @@
     </row>
     <row r="4079">
       <c r="A4079" t="n">
-        <v>334</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4080">
@@ -20962,7 +20962,7 @@
     </row>
     <row r="4107">
       <c r="A4107" t="n">
-        <v>334</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="4108">
@@ -20972,7 +20972,7 @@
     </row>
     <row r="4109">
       <c r="A4109" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4110">
@@ -21007,7 +21007,7 @@
     </row>
     <row r="4116">
       <c r="A4116" t="n">
-        <v>334</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4117">
@@ -21107,7 +21107,7 @@
     </row>
     <row r="4136">
       <c r="A4136" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4137">
@@ -21127,7 +21127,7 @@
     </row>
     <row r="4140">
       <c r="A4140" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4141">
@@ -21187,7 +21187,7 @@
     </row>
     <row r="4152">
       <c r="A4152" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4153">
@@ -21202,7 +21202,7 @@
     </row>
     <row r="4155">
       <c r="A4155" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4156">
@@ -21232,7 +21232,7 @@
     </row>
     <row r="4161">
       <c r="A4161" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4162">
@@ -21317,7 +21317,7 @@
     </row>
     <row r="4178">
       <c r="A4178" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4179">
@@ -21397,7 +21397,7 @@
     </row>
     <row r="4194">
       <c r="A4194" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4195">
@@ -21432,7 +21432,7 @@
     </row>
     <row r="4201">
       <c r="A4201" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4202">
@@ -21592,7 +21592,7 @@
     </row>
     <row r="4233">
       <c r="A4233" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4234">
@@ -21622,7 +21622,7 @@
     </row>
     <row r="4239">
       <c r="A4239" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4240">
@@ -21802,7 +21802,7 @@
     </row>
     <row r="4275">
       <c r="A4275" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4276">
@@ -21812,7 +21812,7 @@
     </row>
     <row r="4277">
       <c r="A4277" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4278">
@@ -21887,7 +21887,7 @@
     </row>
     <row r="4292">
       <c r="A4292" t="n">
-        <v>334</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4293">
@@ -22032,7 +22032,7 @@
     </row>
     <row r="4321">
       <c r="A4321" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4322">
@@ -22207,7 +22207,7 @@
     </row>
     <row r="4356">
       <c r="A4356" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4357">
@@ -22322,7 +22322,7 @@
     </row>
     <row r="4379">
       <c r="A4379" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4380">
@@ -22337,7 +22337,7 @@
     </row>
     <row r="4382">
       <c r="A4382" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4383">
@@ -22362,7 +22362,7 @@
     </row>
     <row r="4387">
       <c r="A4387" t="n">
-        <v>334</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4388">
@@ -22397,7 +22397,7 @@
     </row>
     <row r="4394">
       <c r="A4394" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4395">
@@ -22412,7 +22412,7 @@
     </row>
     <row r="4397">
       <c r="A4397" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4398">
@@ -22452,7 +22452,7 @@
     </row>
     <row r="4405">
       <c r="A4405" t="n">
-        <v>334</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4406">
@@ -22487,7 +22487,7 @@
     </row>
     <row r="4412">
       <c r="A4412" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4413">
@@ -22507,12 +22507,12 @@
     </row>
     <row r="4416">
       <c r="A4416" t="n">
-        <v>334</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4417">
       <c r="A4417" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4418">
@@ -22582,7 +22582,7 @@
     </row>
     <row r="4431">
       <c r="A4431" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4432">
@@ -22642,7 +22642,7 @@
     </row>
     <row r="4443">
       <c r="A4443" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4444">
@@ -22662,7 +22662,7 @@
     </row>
     <row r="4447">
       <c r="A4447" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4448">
@@ -22737,7 +22737,7 @@
     </row>
     <row r="4462">
       <c r="A4462" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4463">
@@ -22867,7 +22867,7 @@
     </row>
     <row r="4488">
       <c r="A4488" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4489">
@@ -22877,7 +22877,7 @@
     </row>
     <row r="4490">
       <c r="A4490" t="n">
-        <v>334</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4491">
@@ -22962,7 +22962,7 @@
     </row>
     <row r="4507">
       <c r="A4507" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4508">
@@ -23007,7 +23007,7 @@
     </row>
     <row r="4516">
       <c r="A4516" t="n">
-        <v>334</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4517">
@@ -23047,7 +23047,7 @@
     </row>
     <row r="4524">
       <c r="A4524" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4525">
@@ -23072,7 +23072,7 @@
     </row>
     <row r="4529">
       <c r="A4529" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4530">
@@ -23287,7 +23287,7 @@
     </row>
     <row r="4572">
       <c r="A4572" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4573">
@@ -23412,7 +23412,7 @@
     </row>
     <row r="4597">
       <c r="A4597" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4598">
@@ -23482,7 +23482,7 @@
     </row>
     <row r="4611">
       <c r="A4611" t="n">
-        <v>334</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4612">
@@ -23607,7 +23607,7 @@
     </row>
     <row r="4636">
       <c r="A4636" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4637">
@@ -23692,7 +23692,7 @@
     </row>
     <row r="4653">
       <c r="A4653" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4654">
@@ -23782,12 +23782,12 @@
     </row>
     <row r="4671">
       <c r="A4671" t="n">
-        <v>334</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4672">
       <c r="A4672" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4673">
@@ -23822,7 +23822,7 @@
     </row>
     <row r="4679">
       <c r="A4679" t="n">
-        <v>334</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="4680">
@@ -24002,7 +24002,7 @@
     </row>
     <row r="4715">
       <c r="A4715" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4716">
@@ -24117,7 +24117,7 @@
     </row>
     <row r="4738">
       <c r="A4738" t="n">
-        <v>334</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4739">
@@ -24177,7 +24177,7 @@
     </row>
     <row r="4750">
       <c r="A4750" t="n">
-        <v>334</v>
+        <v>999</v>
       </c>
     </row>
     <row r="4751">
@@ -24192,7 +24192,7 @@
     </row>
     <row r="4753">
       <c r="A4753" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4754">
@@ -24232,7 +24232,7 @@
     </row>
     <row r="4761">
       <c r="A4761" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4762">
@@ -24332,7 +24332,7 @@
     </row>
     <row r="4781">
       <c r="A4781" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4782">
@@ -24447,7 +24447,7 @@
     </row>
     <row r="4804">
       <c r="A4804" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4805">
@@ -24467,7 +24467,7 @@
     </row>
     <row r="4808">
       <c r="A4808" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4809">
@@ -24682,7 +24682,7 @@
     </row>
     <row r="4851">
       <c r="A4851" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4852">
@@ -24697,7 +24697,7 @@
     </row>
     <row r="4854">
       <c r="A4854" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4855">
@@ -24707,7 +24707,7 @@
     </row>
     <row r="4856">
       <c r="A4856" t="n">
-        <v>334</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4857">
@@ -24727,7 +24727,7 @@
     </row>
     <row r="4860">
       <c r="A4860" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4861">
@@ -24782,7 +24782,7 @@
     </row>
     <row r="4871">
       <c r="A4871" t="n">
-        <v>334</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4872">
@@ -24802,7 +24802,7 @@
     </row>
     <row r="4875">
       <c r="A4875" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4876">
@@ -24852,7 +24852,7 @@
     </row>
     <row r="4885">
       <c r="A4885" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4886">
@@ -24907,12 +24907,12 @@
     </row>
     <row r="4896">
       <c r="A4896" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4897">
       <c r="A4897" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4898">
@@ -24922,7 +24922,7 @@
     </row>
     <row r="4899">
       <c r="A4899" t="n">
-        <v>334</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4900">
@@ -25082,7 +25082,7 @@
     </row>
     <row r="4931">
       <c r="A4931" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4932">
@@ -25117,7 +25117,7 @@
     </row>
     <row r="4938">
       <c r="A4938" t="n">
-        <v>334</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4939">
@@ -25212,7 +25212,7 @@
     </row>
     <row r="4957">
       <c r="A4957" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4958">
@@ -25302,7 +25302,7 @@
     </row>
     <row r="4975">
       <c r="A4975" t="n">
-        <v>334</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="4976">
@@ -25322,7 +25322,7 @@
     </row>
     <row r="4979">
       <c r="A4979" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4980">
@@ -25372,7 +25372,7 @@
     </row>
     <row r="4989">
       <c r="A4989" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4990">
@@ -25587,7 +25587,7 @@
     </row>
     <row r="5032">
       <c r="A5032" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5033">
@@ -25652,7 +25652,7 @@
     </row>
     <row r="5045">
       <c r="A5045" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5046">
@@ -25662,7 +25662,7 @@
     </row>
     <row r="5047">
       <c r="A5047" t="n">
-        <v>334</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5048">
@@ -25687,7 +25687,7 @@
     </row>
     <row r="5052">
       <c r="A5052" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5053">
@@ -25712,7 +25712,7 @@
     </row>
     <row r="5057">
       <c r="A5057" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5058">
@@ -25747,7 +25747,7 @@
     </row>
     <row r="5064">
       <c r="A5064" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5065">
@@ -25807,7 +25807,7 @@
     </row>
     <row r="5076">
       <c r="A5076" t="n">
-        <v>334</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5077">
@@ -25892,7 +25892,7 @@
     </row>
     <row r="5093">
       <c r="A5093" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5094">
@@ -25977,7 +25977,7 @@
     </row>
     <row r="5110">
       <c r="A5110" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5111">
@@ -25992,7 +25992,7 @@
     </row>
     <row r="5113">
       <c r="A5113" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5114">
@@ -26162,7 +26162,7 @@
     </row>
     <row r="5147">
       <c r="A5147" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5148">
@@ -26192,7 +26192,7 @@
     </row>
     <row r="5153">
       <c r="A5153" t="n">
-        <v>334</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="5154">
@@ -26247,12 +26247,12 @@
     </row>
     <row r="5164">
       <c r="A5164" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5165">
       <c r="A5165" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5166">
@@ -26362,7 +26362,7 @@
     </row>
     <row r="5187">
       <c r="A5187" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5188">
@@ -26372,7 +26372,7 @@
     </row>
     <row r="5189">
       <c r="A5189" t="n">
-        <v>334</v>
+        <v>843</v>
       </c>
     </row>
     <row r="5190">
@@ -26497,7 +26497,7 @@
     </row>
     <row r="5214">
       <c r="A5214" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5215">
@@ -26512,7 +26512,7 @@
     </row>
     <row r="5217">
       <c r="A5217" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5218">
@@ -26597,7 +26597,7 @@
     </row>
     <row r="5234">
       <c r="A5234" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5235">
@@ -26612,7 +26612,7 @@
     </row>
     <row r="5237">
       <c r="A5237" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5238">
@@ -26637,12 +26637,12 @@
     </row>
     <row r="5242">
       <c r="A5242" t="n">
-        <v>334</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="5243">
       <c r="A5243" t="n">
-        <v>334</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5244">
@@ -26757,12 +26757,12 @@
     </row>
     <row r="5266">
       <c r="A5266" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="5267">
       <c r="A5267" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5268">
@@ -26827,7 +26827,7 @@
     </row>
     <row r="5280">
       <c r="A5280" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5281">
@@ -26942,7 +26942,7 @@
     </row>
     <row r="5303">
       <c r="A5303" t="n">
-        <v>334</v>
+        <v>690</v>
       </c>
     </row>
     <row r="5304">
@@ -26977,7 +26977,7 @@
     </row>
     <row r="5310">
       <c r="A5310" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5311">
@@ -27022,7 +27022,7 @@
     </row>
     <row r="5319">
       <c r="A5319" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5320">
@@ -27047,7 +27047,7 @@
     </row>
     <row r="5324">
       <c r="A5324" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5325">
@@ -27077,7 +27077,7 @@
     </row>
     <row r="5330">
       <c r="A5330" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5331">
@@ -27292,7 +27292,7 @@
     </row>
     <row r="5373">
       <c r="A5373" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5374">
@@ -27497,7 +27497,7 @@
     </row>
     <row r="5414">
       <c r="A5414" t="n">
-        <v>334</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5415">
@@ -27547,7 +27547,7 @@
     </row>
     <row r="5424">
       <c r="A5424" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5425">
@@ -27582,7 +27582,7 @@
     </row>
     <row r="5431">
       <c r="A5431" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5432">
@@ -27707,7 +27707,7 @@
     </row>
     <row r="5456">
       <c r="A5456" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5457">
@@ -27727,7 +27727,7 @@
     </row>
     <row r="5460">
       <c r="A5460" t="n">
-        <v>334</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5461">
@@ -27937,7 +27937,7 @@
     </row>
     <row r="5502">
       <c r="A5502" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5503">
@@ -27992,7 +27992,7 @@
     </row>
     <row r="5513">
       <c r="A5513" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5514">
@@ -28042,7 +28042,7 @@
     </row>
     <row r="5523">
       <c r="A5523" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5524">
@@ -28067,7 +28067,7 @@
     </row>
     <row r="5528">
       <c r="A5528" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5529">
@@ -28342,7 +28342,7 @@
     </row>
     <row r="5583">
       <c r="A5583" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5584">
@@ -28462,7 +28462,7 @@
     </row>
     <row r="5607">
       <c r="A5607" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5608">
@@ -28472,7 +28472,7 @@
     </row>
     <row r="5609">
       <c r="A5609" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5610">
@@ -28497,12 +28497,12 @@
     </row>
     <row r="5614">
       <c r="A5614" t="n">
-        <v>334</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5615">
       <c r="A5615" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5616">
@@ -28592,7 +28592,7 @@
     </row>
     <row r="5633">
       <c r="A5633" t="n">
-        <v>334</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="5634">
@@ -28737,7 +28737,7 @@
     </row>
     <row r="5662">
       <c r="A5662" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5663">
@@ -28857,7 +28857,7 @@
     </row>
     <row r="5686">
       <c r="A5686" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5687">
@@ -28992,7 +28992,7 @@
     </row>
     <row r="5713">
       <c r="A5713" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5714">
@@ -29227,7 +29227,7 @@
     </row>
     <row r="5760">
       <c r="A5760" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5761">
@@ -29322,7 +29322,7 @@
     </row>
     <row r="5779">
       <c r="A5779" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5780">
@@ -29372,7 +29372,7 @@
     </row>
     <row r="5789">
       <c r="A5789" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5790">
@@ -29547,7 +29547,7 @@
     </row>
     <row r="5824">
       <c r="A5824" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5825">
@@ -29632,7 +29632,7 @@
     </row>
     <row r="5841">
       <c r="A5841" t="n">
-        <v>334</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5842">
@@ -29737,7 +29737,7 @@
     </row>
     <row r="5862">
       <c r="A5862" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5863">
@@ -29802,7 +29802,7 @@
     </row>
     <row r="5875">
       <c r="A5875" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5876">
@@ -29832,7 +29832,7 @@
     </row>
     <row r="5881">
       <c r="A5881" t="n">
-        <v>334</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5882">
@@ -29892,7 +29892,7 @@
     </row>
     <row r="5893">
       <c r="A5893" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5894">
@@ -29912,7 +29912,7 @@
     </row>
     <row r="5897">
       <c r="A5897" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5898">
@@ -30072,7 +30072,7 @@
     </row>
     <row r="5929">
       <c r="A5929" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5930">
@@ -30122,7 +30122,7 @@
     </row>
     <row r="5939">
       <c r="A5939" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5940">
@@ -30162,7 +30162,7 @@
     </row>
     <row r="5947">
       <c r="A5947" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5948">
@@ -30217,12 +30217,12 @@
     </row>
     <row r="5958">
       <c r="A5958" t="n">
-        <v>334</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5959">
       <c r="A5959" t="n">
-        <v>334</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="5960">
@@ -30392,7 +30392,7 @@
     </row>
     <row r="5993">
       <c r="A5993" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5994">
@@ -30482,7 +30482,7 @@
     </row>
     <row r="6011">
       <c r="A6011" t="n">
-        <v>334</v>
+        <v>795</v>
       </c>
     </row>
     <row r="6012">
@@ -30632,7 +30632,7 @@
     </row>
     <row r="6041">
       <c r="A6041" t="n">
-        <v>334</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6042">
@@ -30662,7 +30662,7 @@
     </row>
     <row r="6047">
       <c r="A6047" t="n">
-        <v>334</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6048">
@@ -30752,7 +30752,7 @@
     </row>
     <row r="6065">
       <c r="A6065" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6066">
@@ -30802,7 +30802,7 @@
     </row>
     <row r="6075">
       <c r="A6075" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6076">
@@ -31077,7 +31077,7 @@
     </row>
     <row r="6130">
       <c r="A6130" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6131">
@@ -31137,7 +31137,7 @@
     </row>
     <row r="6142">
       <c r="A6142" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6143">
@@ -31157,7 +31157,7 @@
     </row>
     <row r="6146">
       <c r="A6146" t="n">
-        <v>334</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6147">
@@ -31247,7 +31247,7 @@
     </row>
     <row r="6164">
       <c r="A6164" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6165">
@@ -31412,7 +31412,7 @@
     </row>
     <row r="6197">
       <c r="A6197" t="n">
-        <v>334</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6198">
@@ -31507,7 +31507,7 @@
     </row>
     <row r="6216">
       <c r="A6216" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6217">
@@ -31532,7 +31532,7 @@
     </row>
     <row r="6221">
       <c r="A6221" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6222">
@@ -31717,7 +31717,7 @@
     </row>
     <row r="6258">
       <c r="A6258" t="n">
-        <v>334</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6259">
@@ -31747,7 +31747,7 @@
     </row>
     <row r="6264">
       <c r="A6264" t="n">
-        <v>334</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6265">
@@ -31757,7 +31757,7 @@
     </row>
     <row r="6266">
       <c r="A6266" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6267">
@@ -31802,7 +31802,7 @@
     </row>
     <row r="6275">
       <c r="A6275" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6276">
@@ -31892,7 +31892,7 @@
     </row>
     <row r="6293">
       <c r="A6293" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6294">
@@ -31972,7 +31972,7 @@
     </row>
     <row r="6309">
       <c r="A6309" t="n">
-        <v>334</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="6310">
@@ -32037,7 +32037,7 @@
     </row>
     <row r="6322">
       <c r="A6322" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6323">
@@ -32092,7 +32092,7 @@
     </row>
     <row r="6333">
       <c r="A6333" t="n">
-        <v>334</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6334">
@@ -32142,7 +32142,7 @@
     </row>
     <row r="6343">
       <c r="A6343" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6344">
@@ -32222,7 +32222,7 @@
     </row>
     <row r="6359">
       <c r="A6359" t="n">
-        <v>334</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6360">
@@ -32522,7 +32522,7 @@
     </row>
     <row r="6419">
       <c r="A6419" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6420">
@@ -32682,7 +32682,7 @@
     </row>
     <row r="6451">
       <c r="A6451" t="n">
-        <v>334</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6452">
@@ -32772,7 +32772,7 @@
     </row>
     <row r="6469">
       <c r="A6469" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6470">
@@ -32882,7 +32882,7 @@
     </row>
     <row r="6491">
       <c r="A6491" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6492">
@@ -32992,7 +32992,7 @@
     </row>
     <row r="6513">
       <c r="A6513" t="n">
-        <v>334</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6514">
@@ -33017,7 +33017,7 @@
     </row>
     <row r="6518">
       <c r="A6518" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6519">
@@ -33227,7 +33227,7 @@
     </row>
     <row r="6560">
       <c r="A6560" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6561">
@@ -33237,7 +33237,7 @@
     </row>
     <row r="6562">
       <c r="A6562" t="n">
-        <v>334</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6563">
@@ -33257,12 +33257,12 @@
     </row>
     <row r="6566">
       <c r="A6566" t="n">
-        <v>334</v>
+        <v>595</v>
       </c>
     </row>
     <row r="6567">
       <c r="A6567" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6568">
@@ -33452,7 +33452,7 @@
     </row>
     <row r="6605">
       <c r="A6605" t="n">
-        <v>334</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6606">
@@ -33577,7 +33577,7 @@
     </row>
     <row r="6630">
       <c r="A6630" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6631">
@@ -33637,7 +33637,7 @@
     </row>
     <row r="6642">
       <c r="A6642" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6643">
@@ -33677,7 +33677,7 @@
     </row>
     <row r="6650">
       <c r="A6650" t="n">
-        <v>334</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6651">
@@ -33722,7 +33722,7 @@
     </row>
     <row r="6659">
       <c r="A6659" t="n">
-        <v>334</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6660">
@@ -33747,7 +33747,7 @@
     </row>
     <row r="6664">
       <c r="A6664" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6665">
@@ -33782,7 +33782,7 @@
     </row>
     <row r="6671">
       <c r="A6671" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6672">
@@ -33882,12 +33882,12 @@
     </row>
     <row r="6691">
       <c r="A6691" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6692">
       <c r="A6692" t="n">
-        <v>334</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6693">
@@ -33962,7 +33962,7 @@
     </row>
     <row r="6707">
       <c r="A6707" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6708">
@@ -34002,7 +34002,7 @@
     </row>
     <row r="6715">
       <c r="A6715" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6716">
@@ -34012,7 +34012,7 @@
     </row>
     <row r="6717">
       <c r="A6717" t="n">
-        <v>334</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6718">
@@ -34112,7 +34112,7 @@
     </row>
     <row r="6737">
       <c r="A6737" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6738">
@@ -34207,7 +34207,7 @@
     </row>
     <row r="6756">
       <c r="A6756" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6757">
@@ -34307,7 +34307,7 @@
     </row>
     <row r="6776">
       <c r="A6776" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6777">
@@ -34337,7 +34337,7 @@
     </row>
     <row r="6782">
       <c r="A6782" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6783">
@@ -34372,7 +34372,7 @@
     </row>
     <row r="6789">
       <c r="A6789" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6790">
@@ -34417,7 +34417,7 @@
     </row>
     <row r="6798">
       <c r="A6798" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6799">
@@ -34447,7 +34447,7 @@
     </row>
     <row r="6804">
       <c r="A6804" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6805">
@@ -34512,7 +34512,7 @@
     </row>
     <row r="6817">
       <c r="A6817" t="n">
-        <v>334</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6818">
@@ -34582,7 +34582,7 @@
     </row>
     <row r="6831">
       <c r="A6831" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6832">
@@ -34697,7 +34697,7 @@
     </row>
     <row r="6854">
       <c r="A6854" t="n">
-        <v>334</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="6855">
@@ -34847,7 +34847,7 @@
     </row>
     <row r="6884">
       <c r="A6884" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6885">
@@ -34902,7 +34902,7 @@
     </row>
     <row r="6895">
       <c r="A6895" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6896">
@@ -34932,7 +34932,7 @@
     </row>
     <row r="6901">
       <c r="A6901" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6902">
@@ -35097,7 +35097,7 @@
     </row>
     <row r="6934">
       <c r="A6934" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6935">
@@ -35342,7 +35342,7 @@
     </row>
     <row r="6983">
       <c r="A6983" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6984">
@@ -35352,12 +35352,12 @@
     </row>
     <row r="6985">
       <c r="A6985" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6986">
       <c r="A6986" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6987">
@@ -35442,7 +35442,7 @@
     </row>
     <row r="7003">
       <c r="A7003" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7004">
@@ -35572,7 +35572,7 @@
     </row>
     <row r="7029">
       <c r="A7029" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7030">
@@ -35767,7 +35767,7 @@
     </row>
     <row r="7068">
       <c r="A7068" t="n">
-        <v>334</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7069">
@@ -35837,7 +35837,7 @@
     </row>
     <row r="7082">
       <c r="A7082" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7083">
@@ -35907,7 +35907,7 @@
     </row>
     <row r="7096">
       <c r="A7096" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7097">
@@ -35997,7 +35997,7 @@
     </row>
     <row r="7114">
       <c r="A7114" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7115">
@@ -36022,7 +36022,7 @@
     </row>
     <row r="7119">
       <c r="A7119" t="n">
-        <v>334</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7120">
@@ -36127,7 +36127,7 @@
     </row>
     <row r="7140">
       <c r="A7140" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7141">
@@ -36342,7 +36342,7 @@
     </row>
     <row r="7183">
       <c r="A7183" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7184">
@@ -36542,7 +36542,7 @@
     </row>
     <row r="7223">
       <c r="A7223" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7224">
@@ -36772,7 +36772,7 @@
     </row>
     <row r="7269">
       <c r="A7269" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7270">
@@ -36782,7 +36782,7 @@
     </row>
     <row r="7271">
       <c r="A7271" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7272">
@@ -37087,7 +37087,7 @@
     </row>
     <row r="7332">
       <c r="A7332" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7333">
@@ -37117,7 +37117,7 @@
     </row>
     <row r="7338">
       <c r="A7338" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7339">
@@ -37152,22 +37152,22 @@
     </row>
     <row r="7345">
       <c r="A7345" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7346">
       <c r="A7346" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7347">
       <c r="A7347" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7348">
       <c r="A7348" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7349">
@@ -37187,7 +37187,7 @@
     </row>
     <row r="7352">
       <c r="A7352" t="n">
-        <v>334</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7353">
@@ -37407,7 +37407,7 @@
     </row>
     <row r="7396">
       <c r="A7396" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7397">
@@ -37452,7 +37452,7 @@
     </row>
     <row r="7405">
       <c r="A7405" t="n">
-        <v>334</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7406">
@@ -37552,7 +37552,7 @@
     </row>
     <row r="7425">
       <c r="A7425" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7426">
@@ -37627,7 +37627,7 @@
     </row>
     <row r="7440">
       <c r="A7440" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7441">
@@ -37637,7 +37637,7 @@
     </row>
     <row r="7442">
       <c r="A7442" t="n">
-        <v>334</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7443">
@@ -37662,7 +37662,7 @@
     </row>
     <row r="7447">
       <c r="A7447" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7448">
@@ -37677,7 +37677,7 @@
     </row>
     <row r="7450">
       <c r="A7450" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7451">
@@ -37692,7 +37692,7 @@
     </row>
     <row r="7453">
       <c r="A7453" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7454">
@@ -37747,7 +37747,7 @@
     </row>
     <row r="7464">
       <c r="A7464" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7465">
@@ -37777,7 +37777,7 @@
     </row>
     <row r="7470">
       <c r="A7470" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7471">
@@ -37867,12 +37867,12 @@
     </row>
     <row r="7488">
       <c r="A7488" t="n">
-        <v>334</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7489">
       <c r="A7489" t="n">
-        <v>334</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7490">
@@ -37982,7 +37982,7 @@
     </row>
     <row r="7511">
       <c r="A7511" t="n">
-        <v>334</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7512">
@@ -38052,7 +38052,7 @@
     </row>
     <row r="7525">
       <c r="A7525" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7526">
@@ -38247,7 +38247,7 @@
     </row>
     <row r="7564">
       <c r="A7564" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7565">
@@ -38257,7 +38257,7 @@
     </row>
     <row r="7566">
       <c r="A7566" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7567">
@@ -38357,7 +38357,7 @@
     </row>
     <row r="7586">
       <c r="A7586" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7587">
@@ -38432,7 +38432,7 @@
     </row>
     <row r="7601">
       <c r="A7601" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7602">
@@ -38532,7 +38532,7 @@
     </row>
     <row r="7621">
       <c r="A7621" t="n">
-        <v>334</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7622">
@@ -38597,7 +38597,7 @@
     </row>
     <row r="7634">
       <c r="A7634" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7635">
@@ -38762,7 +38762,7 @@
     </row>
     <row r="7667">
       <c r="A7667" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7668">
@@ -38802,7 +38802,7 @@
     </row>
     <row r="7675">
       <c r="A7675" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7676">
@@ -38867,7 +38867,7 @@
     </row>
     <row r="7688">
       <c r="A7688" t="n">
-        <v>334</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7689">
@@ -39082,7 +39082,7 @@
     </row>
     <row r="7731">
       <c r="A7731" t="n">
-        <v>334</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="7732">
@@ -39272,7 +39272,7 @@
     </row>
     <row r="7769">
       <c r="A7769" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7770">
@@ -39312,12 +39312,12 @@
     </row>
     <row r="7777">
       <c r="A7777" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7778">
       <c r="A7778" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7779">
@@ -39347,7 +39347,7 @@
     </row>
     <row r="7784">
       <c r="A7784" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7785">
@@ -39407,7 +39407,7 @@
     </row>
     <row r="7796">
       <c r="A7796" t="n">
-        <v>334</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7797">
@@ -39422,7 +39422,7 @@
     </row>
     <row r="7799">
       <c r="A7799" t="n">
-        <v>334</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7800">
@@ -39432,7 +39432,7 @@
     </row>
     <row r="7801">
       <c r="A7801" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="7802">
@@ -39527,7 +39527,7 @@
     </row>
     <row r="7820">
       <c r="A7820" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7821">
@@ -39597,7 +39597,7 @@
     </row>
     <row r="7834">
       <c r="A7834" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7835">
@@ -39642,7 +39642,7 @@
     </row>
     <row r="7843">
       <c r="A7843" t="n">
-        <v>334</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7844">
@@ -39652,12 +39652,12 @@
     </row>
     <row r="7845">
       <c r="A7845" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7846">
       <c r="A7846" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7847">
@@ -39682,7 +39682,7 @@
     </row>
     <row r="7851">
       <c r="A7851" t="n">
-        <v>334</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7852">
@@ -39737,7 +39737,7 @@
     </row>
     <row r="7862">
       <c r="A7862" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7863">
@@ -39812,7 +39812,7 @@
     </row>
     <row r="7877">
       <c r="A7877" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7878">
@@ -39822,7 +39822,7 @@
     </row>
     <row r="7879">
       <c r="A7879" t="n">
-        <v>334</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7880">
@@ -39842,7 +39842,7 @@
     </row>
     <row r="7883">
       <c r="A7883" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7884">
@@ -39882,7 +39882,7 @@
     </row>
     <row r="7891">
       <c r="A7891" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7892">
@@ -39987,7 +39987,7 @@
     </row>
     <row r="7912">
       <c r="A7912" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7913">
@@ -40042,7 +40042,7 @@
     </row>
     <row r="7923">
       <c r="A7923" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7924">
@@ -40092,7 +40092,7 @@
     </row>
     <row r="7933">
       <c r="A7933" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7934">
@@ -40207,7 +40207,7 @@
     </row>
     <row r="7956">
       <c r="A7956" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7957">
@@ -40317,7 +40317,7 @@
     </row>
     <row r="7978">
       <c r="A7978" t="n">
-        <v>334</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7979">
@@ -40402,7 +40402,7 @@
     </row>
     <row r="7995">
       <c r="A7995" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7996">
@@ -40482,7 +40482,7 @@
     </row>
     <row r="8011">
       <c r="A8011" t="n">
-        <v>334</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8012">
@@ -40537,7 +40537,7 @@
     </row>
     <row r="8022">
       <c r="A8022" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8023">
@@ -40692,7 +40692,7 @@
     </row>
     <row r="8053">
       <c r="A8053" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8054">
@@ -40717,7 +40717,7 @@
     </row>
     <row r="8058">
       <c r="A8058" t="n">
-        <v>334</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8059">
@@ -40822,7 +40822,7 @@
     </row>
     <row r="8079">
       <c r="A8079" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8080">
@@ -40942,7 +40942,7 @@
     </row>
     <row r="8103">
       <c r="A8103" t="n">
-        <v>334</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8104">
@@ -41027,7 +41027,7 @@
     </row>
     <row r="8120">
       <c r="A8120" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8121">
@@ -41037,7 +41037,7 @@
     </row>
     <row r="8122">
       <c r="A8122" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8123">
@@ -41067,7 +41067,7 @@
     </row>
     <row r="8128">
       <c r="A8128" t="n">
-        <v>334</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8129">
@@ -41122,7 +41122,7 @@
     </row>
     <row r="8139">
       <c r="A8139" t="n">
-        <v>334</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8140">
@@ -41132,7 +41132,7 @@
     </row>
     <row r="8141">
       <c r="A8141" t="n">
-        <v>334</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8142">
@@ -41147,7 +41147,7 @@
     </row>
     <row r="8144">
       <c r="A8144" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8145">
@@ -41202,7 +41202,7 @@
     </row>
     <row r="8155">
       <c r="A8155" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8156">
@@ -41257,7 +41257,7 @@
     </row>
     <row r="8166">
       <c r="A8166" t="n">
-        <v>334</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8167">
@@ -41272,7 +41272,7 @@
     </row>
     <row r="8169">
       <c r="A8169" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8170">
@@ -41282,7 +41282,7 @@
     </row>
     <row r="8171">
       <c r="A8171" t="n">
-        <v>334</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8172">
@@ -41567,12 +41567,12 @@
     </row>
     <row r="8228">
       <c r="A8228" t="n">
-        <v>334</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8229">
       <c r="A8229" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8230">
@@ -41667,7 +41667,7 @@
     </row>
     <row r="8248">
       <c r="A8248" t="n">
-        <v>334</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8249">
@@ -41702,7 +41702,7 @@
     </row>
     <row r="8255">
       <c r="A8255" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8256">
@@ -41762,7 +41762,7 @@
     </row>
     <row r="8267">
       <c r="A8267" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8268">
@@ -41802,7 +41802,7 @@
     </row>
     <row r="8275">
       <c r="A8275" t="n">
-        <v>334</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8276">
@@ -41867,7 +41867,7 @@
     </row>
     <row r="8288">
       <c r="A8288" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8289">
@@ -41937,7 +41937,7 @@
     </row>
     <row r="8302">
       <c r="A8302" t="n">
-        <v>334</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8303">
@@ -41972,7 +41972,7 @@
     </row>
     <row r="8309">
       <c r="A8309" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8310">
@@ -42002,7 +42002,7 @@
     </row>
     <row r="8315">
       <c r="A8315" t="n">
-        <v>334</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8316">
@@ -42052,7 +42052,7 @@
     </row>
     <row r="8325">
       <c r="A8325" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8326">
@@ -42197,7 +42197,7 @@
     </row>
     <row r="8354">
       <c r="A8354" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8355">
@@ -42217,7 +42217,7 @@
     </row>
     <row r="8358">
       <c r="A8358" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8359">
@@ -42292,7 +42292,7 @@
     </row>
     <row r="8373">
       <c r="A8373" t="n">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8374">
@@ -42452,7 +42452,7 @@
     </row>
     <row r="8405">
       <c r="A8405" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8406">
@@ -42602,7 +42602,7 @@
     </row>
     <row r="8435">
       <c r="A8435" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8436">
@@ -42737,7 +42737,7 @@
     </row>
     <row r="8462">
       <c r="A8462" t="n">
-        <v>334</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8463">
@@ -42747,12 +42747,12 @@
     </row>
     <row r="8464">
       <c r="A8464" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8465">
       <c r="A8465" t="n">
-        <v>334</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8466">
@@ -42787,7 +42787,7 @@
     </row>
     <row r="8472">
       <c r="A8472" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8473">
@@ -42852,7 +42852,7 @@
     </row>
     <row r="8485">
       <c r="A8485" t="n">
-        <v>334</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8486">
@@ -42942,7 +42942,7 @@
     </row>
     <row r="8503">
       <c r="A8503" t="n">
-        <v>334</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="8504">
@@ -43047,7 +43047,7 @@
     </row>
     <row r="8524">
       <c r="A8524" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8525">
@@ -43097,7 +43097,7 @@
     </row>
     <row r="8534">
       <c r="A8534" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8535">
@@ -43112,7 +43112,7 @@
     </row>
     <row r="8537">
       <c r="A8537" t="n">
-        <v>334</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8538">
@@ -43222,7 +43222,7 @@
     </row>
     <row r="8559">
       <c r="A8559" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8560">
@@ -43327,7 +43327,7 @@
     </row>
     <row r="8580">
       <c r="A8580" t="n">
-        <v>334</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8581">
@@ -43357,7 +43357,7 @@
     </row>
     <row r="8586">
       <c r="A8586" t="n">
-        <v>334</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8587">
@@ -43497,7 +43497,7 @@
     </row>
     <row r="8614">
       <c r="A8614" t="n">
-        <v>334</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8615">
@@ -43522,7 +43522,7 @@
     </row>
     <row r="8619">
       <c r="A8619" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8620">
@@ -43867,7 +43867,7 @@
     </row>
     <row r="8688">
       <c r="A8688" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8689">
@@ -44062,7 +44062,7 @@
     </row>
     <row r="8727">
       <c r="A8727" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8728">
@@ -44132,7 +44132,7 @@
     </row>
     <row r="8741">
       <c r="A8741" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8742">
@@ -44247,7 +44247,7 @@
     </row>
     <row r="8764">
       <c r="A8764" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8765">
@@ -44377,7 +44377,7 @@
     </row>
     <row r="8790">
       <c r="A8790" t="n">
-        <v>334</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8791">
@@ -44547,7 +44547,7 @@
     </row>
     <row r="8824">
       <c r="A8824" t="n">
-        <v>334</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8825">
@@ -45142,7 +45142,7 @@
     </row>
     <row r="8943">
       <c r="A8943" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8944">
@@ -45357,7 +45357,7 @@
     </row>
     <row r="8986">
       <c r="A8986" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8987">
@@ -45402,7 +45402,7 @@
     </row>
     <row r="8995">
       <c r="A8995" t="n">
-        <v>334</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8996">
@@ -45447,7 +45447,7 @@
     </row>
     <row r="9004">
       <c r="A9004" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9005">
@@ -45527,7 +45527,7 @@
     </row>
     <row r="9020">
       <c r="A9020" t="n">
-        <v>334</v>
+        <v>848</v>
       </c>
     </row>
     <row r="9021">
@@ -45542,7 +45542,7 @@
     </row>
     <row r="9023">
       <c r="A9023" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9024">
@@ -45727,7 +45727,7 @@
     </row>
     <row r="9060">
       <c r="A9060" t="n">
-        <v>334</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9061">
@@ -45962,7 +45962,7 @@
     </row>
     <row r="9107">
       <c r="A9107" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9108">
@@ -46127,7 +46127,7 @@
     </row>
     <row r="9140">
       <c r="A9140" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9141">
@@ -46202,7 +46202,7 @@
     </row>
     <row r="9155">
       <c r="A9155" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9156">
@@ -46237,7 +46237,7 @@
     </row>
     <row r="9162">
       <c r="A9162" t="n">
-        <v>334</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9163">
@@ -46287,7 +46287,7 @@
     </row>
     <row r="9172">
       <c r="A9172" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9173">
@@ -46302,7 +46302,7 @@
     </row>
     <row r="9175">
       <c r="A9175" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9176">
@@ -46347,12 +46347,12 @@
     </row>
     <row r="9184">
       <c r="A9184" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9185">
       <c r="A9185" t="n">
-        <v>334</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9186">
@@ -46597,7 +46597,7 @@
     </row>
     <row r="9234">
       <c r="A9234" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9235">
@@ -46617,12 +46617,12 @@
     </row>
     <row r="9238">
       <c r="A9238" t="n">
-        <v>334</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9239">
       <c r="A9239" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9240">
@@ -46667,7 +46667,7 @@
     </row>
     <row r="9248">
       <c r="A9248" t="n">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9249">
@@ -46712,7 +46712,7 @@
     </row>
     <row r="9257">
       <c r="A9257" t="n">
-        <v>334</v>
+        <v>799</v>
       </c>
     </row>
     <row r="9258">
@@ -46857,7 +46857,7 @@
     </row>
     <row r="9286">
       <c r="A9286" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9287">
@@ -46872,7 +46872,7 @@
     </row>
     <row r="9289">
       <c r="A9289" t="n">
-        <v>334</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9290">
@@ -47012,7 +47012,7 @@
     </row>
     <row r="9317">
       <c r="A9317" t="n">
-        <v>334</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9318">
@@ -47087,7 +47087,7 @@
     </row>
     <row r="9332">
       <c r="A9332" t="n">
-        <v>334</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9333">
@@ -47187,7 +47187,7 @@
     </row>
     <row r="9352">
       <c r="A9352" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9353">
@@ -47277,7 +47277,7 @@
     </row>
     <row r="9370">
       <c r="A9370" t="n">
-        <v>334</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9371">
@@ -47312,7 +47312,7 @@
     </row>
     <row r="9377">
       <c r="A9377" t="n">
-        <v>334</v>
+        <v>945</v>
       </c>
     </row>
     <row r="9378">
@@ -47377,7 +47377,7 @@
     </row>
     <row r="9390">
       <c r="A9390" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9391">
@@ -47497,7 +47497,7 @@
     </row>
     <row r="9414">
       <c r="A9414" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9415">
@@ -47557,7 +47557,7 @@
     </row>
     <row r="9426">
       <c r="A9426" t="n">
-        <v>334</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9427">
@@ -47572,7 +47572,7 @@
     </row>
     <row r="9429">
       <c r="A9429" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9430">
@@ -47632,7 +47632,7 @@
     </row>
     <row r="9441">
       <c r="A9441" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9442">
@@ -47657,7 +47657,7 @@
     </row>
     <row r="9446">
       <c r="A9446" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9447">
@@ -47682,7 +47682,7 @@
     </row>
     <row r="9451">
       <c r="A9451" t="n">
-        <v>334</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="9452">
@@ -47807,7 +47807,7 @@
     </row>
     <row r="9476">
       <c r="A9476" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9477">
@@ -48092,7 +48092,7 @@
     </row>
     <row r="9533">
       <c r="A9533" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9534">
@@ -48177,7 +48177,7 @@
     </row>
     <row r="9550">
       <c r="A9550" t="n">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9551">
@@ -48202,7 +48202,7 @@
     </row>
     <row r="9555">
       <c r="A9555" t="n">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9556">
@@ -48272,7 +48272,7 @@
     </row>
     <row r="9569">
       <c r="A9569" t="n">
-        <v>334</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9570">
@@ -48317,7 +48317,7 @@
     </row>
     <row r="9578">
       <c r="A9578" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9579">
@@ -48402,7 +48402,7 @@
     </row>
     <row r="9595">
       <c r="A9595" t="n">
-        <v>334</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="9596">
@@ -48417,7 +48417,7 @@
     </row>
     <row r="9598">
       <c r="A9598" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9599">
@@ -48627,7 +48627,7 @@
     </row>
     <row r="9640">
       <c r="A9640" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9641">
@@ -48717,7 +48717,7 @@
     </row>
     <row r="9658">
       <c r="A9658" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9659">
@@ -48747,7 +48747,7 @@
     </row>
     <row r="9664">
       <c r="A9664" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9665">
@@ -48817,7 +48817,7 @@
     </row>
     <row r="9678">
       <c r="A9678" t="n">
-        <v>334</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9679">
@@ -48827,7 +48827,7 @@
     </row>
     <row r="9680">
       <c r="A9680" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9681">
@@ -48932,7 +48932,7 @@
     </row>
     <row r="9701">
       <c r="A9701" t="n">
-        <v>334</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9702">
@@ -48942,7 +48942,7 @@
     </row>
     <row r="9703">
       <c r="A9703" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9704">
@@ -48977,7 +48977,7 @@
     </row>
     <row r="9710">
       <c r="A9710" t="n">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9711">
@@ -49077,7 +49077,7 @@
     </row>
     <row r="9730">
       <c r="A9730" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9731">
@@ -49117,7 +49117,7 @@
     </row>
     <row r="9738">
       <c r="A9738" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9739">
@@ -49252,7 +49252,7 @@
     </row>
     <row r="9765">
       <c r="A9765" t="n">
-        <v>334</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9766">
@@ -49307,7 +49307,7 @@
     </row>
     <row r="9776">
       <c r="A9776" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9777">
